--- a/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/20gps/1mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/20gps/1mps_analysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Time</t>
   </si>
@@ -79,13 +79,34 @@
     <t>Q</t>
   </si>
   <si>
-    <t>rolling_std</t>
-  </si>
-  <si>
     <t>steady_state</t>
   </si>
   <si>
-    <t>avg_Q_steady</t>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>RTD_OUT_unc</t>
+  </si>
+  <si>
+    <t>RTD_IN_unc</t>
+  </si>
+  <si>
+    <t>RTD_unc</t>
+  </si>
+  <si>
+    <t>Delta_RTD</t>
+  </si>
+  <si>
+    <t>Rel_unc</t>
+  </si>
+  <si>
+    <t>ABS_unc</t>
+  </si>
+  <si>
+    <t>Average Q (W)</t>
+  </si>
+  <si>
+    <t>Average Q Uncertainty (W)</t>
   </si>
 </sst>
 </file>
@@ -421,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X31"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,8 +518,23 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:29">
       <c r="A2" s="1">
         <v>46068.61545935185</v>
       </c>
@@ -562,14 +598,32 @@
       <c r="U2">
         <v>227.9587871042666</v>
       </c>
-      <c r="W2" t="b">
-        <v>0</v>
+      <c r="V2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
+        <v>29</v>
       </c>
       <c r="X2">
-        <v>221.3957719718514</v>
+        <v>0.257495904</v>
+      </c>
+      <c r="Y2">
+        <v>0.262617938</v>
+      </c>
+      <c r="Z2">
+        <v>0.3677938579369551</v>
+      </c>
+      <c r="AA2">
+        <v>2.561017</v>
+      </c>
+      <c r="AB2">
+        <v>0.1439601617707731</v>
+      </c>
+      <c r="AC2">
+        <v>32.81698386859945</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:29">
       <c r="A3" s="1">
         <v>46068.6155756713</v>
       </c>
@@ -633,11 +687,32 @@
       <c r="U3">
         <v>225.8412366945132</v>
       </c>
-      <c r="W3" t="b">
-        <v>0</v>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>222.8496763553217</v>
+      </c>
+      <c r="X3">
+        <v>0.257541716</v>
+      </c>
+      <c r="Y3">
+        <v>0.26262908</v>
+      </c>
+      <c r="Z3">
+        <v>0.3678338879737307</v>
+      </c>
+      <c r="AA3">
+        <v>2.543682000000004</v>
+      </c>
+      <c r="AB3">
+        <v>0.1449522209551644</v>
+      </c>
+      <c r="AC3">
+        <v>32.73618884213064</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>46068.61569199074</v>
       </c>
@@ -701,14 +776,32 @@
       <c r="U4">
         <v>226.6887810614229</v>
       </c>
-      <c r="V4">
-        <v>1.065775659679111</v>
-      </c>
-      <c r="W4" t="b">
+      <c r="V4" t="b">
         <v>1</v>
       </c>
+      <c r="W4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4">
+        <v>0.257555076</v>
+      </c>
+      <c r="Y4">
+        <v>0.262632582</v>
+      </c>
+      <c r="Z4">
+        <v>0.3678457425353086</v>
+      </c>
+      <c r="AA4">
+        <v>2.538753</v>
+      </c>
+      <c r="AB4">
+        <v>0.1452369665656355</v>
+      </c>
+      <c r="AC4">
+        <v>32.92359091582256</v>
+      </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>46068.61580773148</v>
       </c>
@@ -772,14 +865,32 @@
       <c r="U5">
         <v>225.9713288085688</v>
       </c>
-      <c r="V5">
-        <v>0.4564342134315375</v>
-      </c>
-      <c r="W5" t="b">
+      <c r="V5" t="b">
         <v>1</v>
       </c>
+      <c r="W5">
+        <v>32.77362820046438</v>
+      </c>
+      <c r="X5">
+        <v>0.257557622</v>
+      </c>
+      <c r="Y5">
+        <v>0.262639904</v>
+      </c>
+      <c r="Z5">
+        <v>0.3678527529099437</v>
+      </c>
+      <c r="AA5">
+        <v>2.541141000000003</v>
+      </c>
+      <c r="AB5">
+        <v>0.1451038817859258</v>
+      </c>
+      <c r="AC5">
+        <v>32.78931698244713</v>
+      </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>46068.61592405092</v>
       </c>
@@ -843,14 +954,29 @@
       <c r="U6">
         <v>224.8910098609066</v>
       </c>
-      <c r="V6">
-        <v>0.9049685126391026</v>
-      </c>
-      <c r="W6" t="b">
+      <c r="V6" t="b">
         <v>1</v>
       </c>
+      <c r="X6">
+        <v>0.25758339</v>
+      </c>
+      <c r="Y6">
+        <v>0.262652956</v>
+      </c>
+      <c r="Z6">
+        <v>0.3678801137591295</v>
+      </c>
+      <c r="AA6">
+        <v>2.534783000000004</v>
+      </c>
+      <c r="AB6">
+        <v>0.1454768882223231</v>
+      </c>
+      <c r="AC6">
+        <v>32.71644430374047</v>
+      </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:29">
       <c r="A7" s="1">
         <v>46068.61604037037</v>
       </c>
@@ -914,14 +1040,29 @@
       <c r="U7">
         <v>224.6778679284893</v>
       </c>
-      <c r="V7">
-        <v>0.6934887117956806</v>
-      </c>
-      <c r="W7" t="b">
+      <c r="V7" t="b">
         <v>1</v>
       </c>
+      <c r="X7">
+        <v>0.257610432</v>
+      </c>
+      <c r="Y7">
+        <v>0.262658368</v>
+      </c>
+      <c r="Z7">
+        <v>0.3679029124044142</v>
+      </c>
+      <c r="AA7">
+        <v>2.523967999999996</v>
+      </c>
+      <c r="AB7">
+        <v>0.1461063174938991</v>
+      </c>
+      <c r="AC7">
+        <v>32.82685590541219</v>
+      </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:29">
       <c r="A8" s="1">
         <v>46068.61615668982</v>
       </c>
@@ -985,14 +1126,29 @@
       <c r="U8">
         <v>225.8799674807235</v>
       </c>
-      <c r="V8">
-        <v>0.6414189986051253</v>
-      </c>
-      <c r="W8" t="b">
+      <c r="V8" t="b">
         <v>1</v>
       </c>
+      <c r="X8">
+        <v>0.25761075</v>
+      </c>
+      <c r="Y8">
+        <v>0.262664418</v>
+      </c>
+      <c r="Z8">
+        <v>0.3679074543942283</v>
+      </c>
+      <c r="AA8">
+        <v>2.526834000000001</v>
+      </c>
+      <c r="AB8">
+        <v>0.1459431699751881</v>
+      </c>
+      <c r="AC8">
+        <v>32.96563848802918</v>
+      </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>46068.61627243055</v>
       </c>
@@ -1056,14 +1212,29 @@
       <c r="U9">
         <v>222.8666435171125</v>
       </c>
-      <c r="V9">
-        <v>1.516888180427285</v>
-      </c>
-      <c r="W9" t="b">
+      <c r="V9" t="b">
         <v>1</v>
       </c>
+      <c r="X9">
+        <v>0.257630474</v>
+      </c>
+      <c r="Y9">
+        <v>0.262668238</v>
+      </c>
+      <c r="Z9">
+        <v>0.3679239926771416</v>
+      </c>
+      <c r="AA9">
+        <v>2.518881999999998</v>
+      </c>
+      <c r="AB9">
+        <v>0.1464082967988744</v>
+      </c>
+      <c r="AC9">
+        <v>32.62952569062236</v>
+      </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:29">
       <c r="A10" s="1">
         <v>46068.61638817129</v>
       </c>
@@ -1127,14 +1298,29 @@
       <c r="U10">
         <v>223.9783649591244</v>
       </c>
-      <c r="V10">
-        <v>1.523818560090193</v>
-      </c>
-      <c r="W10" t="b">
+      <c r="V10" t="b">
         <v>1</v>
       </c>
+      <c r="X10">
+        <v>0.257632382</v>
+      </c>
+      <c r="Y10">
+        <v>0.262673012</v>
+      </c>
+      <c r="Z10">
+        <v>0.3679287369697372</v>
+      </c>
+      <c r="AA10">
+        <v>2.520314999999997</v>
+      </c>
+      <c r="AB10">
+        <v>0.1463273184918805</v>
+      </c>
+      <c r="AC10">
+        <v>32.77415354466444</v>
+      </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:29">
       <c r="A11" s="1">
         <v>46068.61650449074</v>
       </c>
@@ -1198,14 +1384,29 @@
       <c r="U11">
         <v>222.6153845366752</v>
       </c>
-      <c r="V11">
-        <v>0.7253471894959522</v>
-      </c>
-      <c r="W11" t="b">
+      <c r="V11" t="b">
         <v>1</v>
       </c>
+      <c r="X11">
+        <v>0.257652108</v>
+      </c>
+      <c r="Y11">
+        <v>0.26266951</v>
+      </c>
+      <c r="Z11">
+        <v>0.3679400497913808</v>
+      </c>
+      <c r="AA11">
+        <v>2.508701000000002</v>
+      </c>
+      <c r="AB11">
+        <v>0.1470060814434575</v>
+      </c>
+      <c r="AC11">
+        <v>32.72581534976509</v>
+      </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:29">
       <c r="A12" s="1">
         <v>46068.61662023148</v>
       </c>
@@ -1269,14 +1470,29 @@
       <c r="U12">
         <v>222.899255124203</v>
       </c>
-      <c r="V12">
-        <v>0.7191170718626917</v>
-      </c>
-      <c r="W12" t="b">
+      <c r="V12" t="b">
         <v>1</v>
       </c>
+      <c r="X12">
+        <v>0.257651152</v>
+      </c>
+      <c r="Y12">
+        <v>0.262672694</v>
+      </c>
+      <c r="Z12">
+        <v>0.367941653391057</v>
+      </c>
+      <c r="AA12">
+        <v>2.510771000000005</v>
+      </c>
+      <c r="AB12">
+        <v>0.1468860808435471</v>
+      </c>
+      <c r="AC12">
+        <v>32.74079800814012</v>
+      </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:29">
       <c r="A13" s="1">
         <v>46068.61673597222</v>
       </c>
@@ -1340,14 +1556,29 @@
       <c r="U13">
         <v>223.4095945920072</v>
       </c>
-      <c r="V13">
-        <v>0.4024505134902673</v>
-      </c>
-      <c r="W13" t="b">
+      <c r="V13" t="b">
         <v>1</v>
       </c>
+      <c r="X13">
+        <v>0.257655606</v>
+      </c>
+      <c r="Y13">
+        <v>0.262668874</v>
+      </c>
+      <c r="Z13">
+        <v>0.3679420452620971</v>
+      </c>
+      <c r="AA13">
+        <v>2.506633999999998</v>
+      </c>
+      <c r="AB13">
+        <v>0.1471275379220552</v>
+      </c>
+      <c r="AC13">
+        <v>32.86970360048652</v>
+      </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:29">
       <c r="A14" s="1">
         <v>46068.61685229166</v>
       </c>
@@ -1411,14 +1642,29 @@
       <c r="U14">
         <v>222.505838416199</v>
       </c>
-      <c r="V14">
-        <v>0.4531369005510025</v>
-      </c>
-      <c r="W14" t="b">
+      <c r="V14" t="b">
         <v>1</v>
       </c>
+      <c r="X14">
+        <v>0.257647016</v>
+      </c>
+      <c r="Y14">
+        <v>0.26266792</v>
+      </c>
+      <c r="Z14">
+        <v>0.3679353490096197</v>
+      </c>
+      <c r="AA14">
+        <v>2.510452000000001</v>
+      </c>
+      <c r="AB14">
+        <v>0.1469021535430162</v>
+      </c>
+      <c r="AC14">
+        <v>32.68658683923401</v>
+      </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:29">
       <c r="A15" s="1">
         <v>46068.61696861111</v>
       </c>
@@ -1482,14 +1728,29 @@
       <c r="U15">
         <v>221.6771425735375</v>
       </c>
-      <c r="V15">
-        <v>0.8664969726100836</v>
-      </c>
-      <c r="W15" t="b">
+      <c r="V15" t="b">
         <v>1</v>
       </c>
+      <c r="X15">
+        <v>0.257650834</v>
+      </c>
+      <c r="Y15">
+        <v>0.262657732</v>
+      </c>
+      <c r="Z15">
+        <v>0.3679307495171875</v>
+      </c>
+      <c r="AA15">
+        <v>2.503448999999996</v>
+      </c>
+      <c r="AB15">
+        <v>0.1473093543281918</v>
+      </c>
+      <c r="AC15">
+        <v>32.65511674182631</v>
+      </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:29">
       <c r="A16" s="1">
         <v>46068.61708493056</v>
       </c>
@@ -1553,14 +1814,29 @@
       <c r="U16">
         <v>222.692508424132</v>
       </c>
-      <c r="V16">
-        <v>0.5404551017519698</v>
-      </c>
-      <c r="W16" t="b">
+      <c r="V16" t="b">
         <v>1</v>
       </c>
+      <c r="X16">
+        <v>0.257637792</v>
+      </c>
+      <c r="Y16">
+        <v>0.262652956</v>
+      </c>
+      <c r="Z16">
+        <v>0.3679182071631862</v>
+      </c>
+      <c r="AA16">
+        <v>2.507581999999999</v>
+      </c>
+      <c r="AB16">
+        <v>0.1470626884481097</v>
+      </c>
+      <c r="AC16">
+        <v>32.74975898610618</v>
+      </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:29">
       <c r="A17" s="1">
         <v>46068.61720067129</v>
       </c>
@@ -1624,14 +1900,29 @@
       <c r="U17">
         <v>221.8760241434912</v>
       </c>
-      <c r="V17">
-        <v>0.5380781030595351</v>
-      </c>
-      <c r="W17" t="b">
+      <c r="V17" t="b">
         <v>1</v>
       </c>
+      <c r="X17">
+        <v>0.257641926</v>
+      </c>
+      <c r="Y17">
+        <v>0.262647226</v>
+      </c>
+      <c r="Z17">
+        <v>0.3679170115100477</v>
+      </c>
+      <c r="AA17">
+        <v>2.502650000000003</v>
+      </c>
+      <c r="AB17">
+        <v>0.1473506911228125</v>
+      </c>
+      <c r="AC17">
+        <v>32.69358550112526</v>
+      </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:29">
       <c r="A18" s="1">
         <v>46068.61731641203</v>
       </c>
@@ -1695,14 +1986,29 @@
       <c r="U18">
         <v>223.0731176349567</v>
       </c>
-      <c r="V18">
-        <v>0.611629351160475</v>
-      </c>
-      <c r="W18" t="b">
+      <c r="V18" t="b">
         <v>1</v>
       </c>
+      <c r="X18">
+        <v>0.257643836</v>
+      </c>
+      <c r="Y18">
+        <v>0.262646272</v>
+      </c>
+      <c r="Z18">
+        <v>0.3679176679969214</v>
+      </c>
+      <c r="AA18">
+        <v>2.501218000000001</v>
+      </c>
+      <c r="AB18">
+        <v>0.1474349259277377</v>
+      </c>
+      <c r="AC18">
+        <v>32.88876857497936</v>
+      </c>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:29">
       <c r="A19" s="1">
         <v>46068.61743273148</v>
       </c>
@@ -1766,14 +2072,29 @@
       <c r="U19">
         <v>221.8762762063018</v>
       </c>
-      <c r="V19">
-        <v>0.6910694967690739</v>
-      </c>
-      <c r="W19" t="b">
+      <c r="V19" t="b">
         <v>1</v>
       </c>
+      <c r="X19">
+        <v>0.257655924</v>
+      </c>
+      <c r="Y19">
+        <v>0.262652638</v>
+      </c>
+      <c r="Z19">
+        <v>0.3679306774660857</v>
+      </c>
+      <c r="AA19">
+        <v>2.498356999999999</v>
+      </c>
+      <c r="AB19">
+        <v>0.1476081803865757</v>
+      </c>
+      <c r="AC19">
+        <v>32.7507534017615</v>
+      </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:29">
       <c r="A20" s="1">
         <v>46068.61754905093</v>
       </c>
@@ -1837,14 +2158,29 @@
       <c r="U20">
         <v>221.5236396608814</v>
       </c>
-      <c r="V20">
-        <v>0.8121641798977187</v>
-      </c>
-      <c r="W20" t="b">
+      <c r="V20" t="b">
         <v>1</v>
       </c>
+      <c r="X20">
+        <v>0.257665468</v>
+      </c>
+      <c r="Y20">
+        <v>0.262653276</v>
+      </c>
+      <c r="Z20">
+        <v>0.3679378164760877</v>
+      </c>
+      <c r="AA20">
+        <v>2.493904000000001</v>
+      </c>
+      <c r="AB20">
+        <v>0.147873390194132</v>
+      </c>
+      <c r="AC20">
+        <v>32.75745160479781</v>
+      </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:29">
       <c r="A21" s="1">
         <v>46068.61766537037</v>
       </c>
@@ -1908,14 +2244,29 @@
       <c r="U21">
         <v>223.2597650736147</v>
       </c>
-      <c r="V21">
-        <v>0.9176532958114346</v>
-      </c>
-      <c r="W21" t="b">
+      <c r="V21" t="b">
         <v>1</v>
       </c>
+      <c r="X21">
+        <v>0.25767374</v>
+      </c>
+      <c r="Y21">
+        <v>0.262653594</v>
+      </c>
+      <c r="Z21">
+        <v>0.3679438363754779</v>
+      </c>
+      <c r="AA21">
+        <v>2.489927000000002</v>
+      </c>
+      <c r="AB21">
+        <v>0.1481109117387518</v>
+      </c>
+      <c r="AC21">
+        <v>33.06720735963261</v>
+      </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:29">
       <c r="A22" s="1">
         <v>46068.61778111111</v>
       </c>
@@ -1979,14 +2330,29 @@
       <c r="U22">
         <v>221.0246625069869</v>
       </c>
-      <c r="V22">
-        <v>1.173228674228489</v>
-      </c>
-      <c r="W22" t="b">
+      <c r="V22" t="b">
         <v>1</v>
       </c>
+      <c r="X22">
+        <v>0.257656242</v>
+      </c>
+      <c r="Y22">
+        <v>0.262648818</v>
+      </c>
+      <c r="Z22">
+        <v>0.3679281732055317</v>
+      </c>
+      <c r="AA22">
+        <v>2.496288</v>
+      </c>
+      <c r="AB22">
+        <v>0.147728960401766</v>
+      </c>
+      <c r="AC22">
+        <v>32.65174361530836</v>
+      </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:29">
       <c r="A23" s="1">
         <v>46068.61789743056</v>
       </c>
@@ -2050,14 +2416,29 @@
       <c r="U23">
         <v>221.8132919069531</v>
       </c>
-      <c r="V23">
-        <v>1.133571379586642</v>
-      </c>
-      <c r="W23" t="b">
+      <c r="V23" t="b">
         <v>1</v>
       </c>
+      <c r="X23">
+        <v>0.25766865</v>
+      </c>
+      <c r="Y23">
+        <v>0.262642452</v>
+      </c>
+      <c r="Z23">
+        <v>0.3679323182127316</v>
+      </c>
+      <c r="AA23">
+        <v>2.486901000000003</v>
+      </c>
+      <c r="AB23">
+        <v>0.1482856874329431</v>
+      </c>
+      <c r="AC23">
+        <v>32.89173647218661</v>
+      </c>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:29">
       <c r="A24" s="1">
         <v>46068.6180131713</v>
       </c>
@@ -2121,14 +2502,29 @@
       <c r="U24">
         <v>221.6821464101943</v>
       </c>
-      <c r="V24">
-        <v>0.4225755464581509</v>
-      </c>
-      <c r="W24" t="b">
+      <c r="V24" t="b">
         <v>1</v>
       </c>
+      <c r="X24">
+        <v>0.257668968</v>
+      </c>
+      <c r="Y24">
+        <v>0.262642134</v>
+      </c>
+      <c r="Z24">
+        <v>0.3679323139142022</v>
+      </c>
+      <c r="AA24">
+        <v>2.486582999999996</v>
+      </c>
+      <c r="AB24">
+        <v>0.1483045631843662</v>
+      </c>
+      <c r="AC24">
+        <v>32.87647388913658</v>
+      </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:29">
       <c r="A25" s="1">
         <v>46068.61812949074</v>
       </c>
@@ -2192,14 +2588,29 @@
       <c r="U25">
         <v>219.0241821619565</v>
       </c>
-      <c r="V25">
-        <v>1.573801462270237</v>
-      </c>
-      <c r="W25" t="b">
+      <c r="V25" t="b">
         <v>1</v>
       </c>
+      <c r="X25">
+        <v>0.257672468</v>
+      </c>
+      <c r="Y25">
+        <v>0.262643406</v>
+      </c>
+      <c r="Z25">
+        <v>0.3679356730197439</v>
+      </c>
+      <c r="AA25">
+        <v>2.485469000000002</v>
+      </c>
+      <c r="AB25">
+        <v>0.1483720803255428</v>
+      </c>
+      <c r="AC25">
+        <v>32.49707354897012</v>
+      </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:29">
       <c r="A26" s="1">
         <v>46068.61824523148</v>
       </c>
@@ -2263,14 +2674,29 @@
       <c r="U26">
         <v>220.8609456659351</v>
       </c>
-      <c r="V26">
-        <v>1.360933795648428</v>
-      </c>
-      <c r="W26" t="b">
+      <c r="V26" t="b">
         <v>1</v>
       </c>
+      <c r="X26">
+        <v>0.257664196</v>
+      </c>
+      <c r="Y26">
+        <v>0.262638312</v>
+      </c>
+      <c r="Z26">
+        <v>0.3679262437371595</v>
+      </c>
+      <c r="AA26">
+        <v>2.487057999999998</v>
+      </c>
+      <c r="AB26">
+        <v>0.148273932331935</v>
+      </c>
+      <c r="AC26">
+        <v>32.74792091243804</v>
+      </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:29">
       <c r="A27" s="1">
         <v>46068.61836155093</v>
       </c>
@@ -2334,14 +2760,29 @@
       <c r="U27">
         <v>220.7519767079542</v>
       </c>
-      <c r="V27">
-        <v>1.030440714494593</v>
-      </c>
-      <c r="W27" t="b">
+      <c r="V27" t="b">
         <v>1</v>
       </c>
+      <c r="X27">
+        <v>0.257658788</v>
+      </c>
+      <c r="Y27">
+        <v>0.262629718</v>
+      </c>
+      <c r="Z27">
+        <v>0.3679163217504606</v>
+      </c>
+      <c r="AA27">
+        <v>2.485464999999998</v>
+      </c>
+      <c r="AB27">
+        <v>0.1483645499547461</v>
+      </c>
+      <c r="AC27">
+        <v>32.75176767589622</v>
+      </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:29">
       <c r="A28" s="1">
         <v>46068.61847787037</v>
       </c>
@@ -2405,14 +2846,29 @@
       <c r="U28">
         <v>220.2865616996705</v>
       </c>
-      <c r="V28">
-        <v>0.3050689278505098</v>
-      </c>
-      <c r="W28" t="b">
+      <c r="V28" t="b">
         <v>1</v>
       </c>
+      <c r="X28">
+        <v>0.25765847</v>
+      </c>
+      <c r="Y28">
+        <v>0.26263099</v>
+      </c>
+      <c r="Z28">
+        <v>0.3679170070425136</v>
+      </c>
+      <c r="AA28">
+        <v>2.486260000000001</v>
+      </c>
+      <c r="AB28">
+        <v>0.1483175998542104</v>
+      </c>
+      <c r="AC28">
+        <v>32.67237411143156</v>
+      </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:29">
       <c r="A29" s="1">
         <v>46068.61859418981</v>
       </c>
@@ -2476,14 +2932,29 @@
       <c r="U29">
         <v>221.8216257576969</v>
       </c>
-      <c r="V29">
-        <v>0.78710247975236</v>
-      </c>
-      <c r="W29" t="b">
+      <c r="V29" t="b">
         <v>1</v>
       </c>
+      <c r="X29">
+        <v>0.257661014</v>
+      </c>
+      <c r="Y29">
+        <v>0.262635766</v>
+      </c>
+      <c r="Z29">
+        <v>0.367922197914063</v>
+      </c>
+      <c r="AA29">
+        <v>2.487376000000005</v>
+      </c>
+      <c r="AB29">
+        <v>0.148253439556485</v>
+      </c>
+      <c r="AC29">
+        <v>32.88581898658997</v>
+      </c>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:29">
       <c r="A30" s="1">
         <v>46068.61871050926</v>
       </c>
@@ -2547,14 +3018,29 @@
       <c r="U30">
         <v>221.7782011446523</v>
       </c>
-      <c r="V30">
-        <v>0.8740037750763339</v>
-      </c>
-      <c r="W30" t="b">
+      <c r="V30" t="b">
         <v>1</v>
       </c>
+      <c r="X30">
+        <v>0.257653698</v>
+      </c>
+      <c r="Y30">
+        <v>0.262636722</v>
+      </c>
+      <c r="Z30">
+        <v>0.3679177568913744</v>
+      </c>
+      <c r="AA30">
+        <v>2.491512</v>
+      </c>
+      <c r="AB30">
+        <v>0.1480066757542005</v>
+      </c>
+      <c r="AC30">
+        <v>32.8246543061664</v>
+      </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:29">
       <c r="A31" s="1">
         <v>46068.61882625</v>
       </c>
@@ -2618,11 +3104,26 @@
       <c r="U31">
         <v>220.2841628965245</v>
       </c>
-      <c r="V31">
-        <v>0.8753882979730825</v>
-      </c>
-      <c r="W31" t="b">
+      <c r="V31" t="b">
         <v>1</v>
+      </c>
+      <c r="X31">
+        <v>0.25765688</v>
+      </c>
+      <c r="Y31">
+        <v>0.262633538</v>
+      </c>
+      <c r="Z31">
+        <v>0.3679177123946764</v>
+      </c>
+      <c r="AA31">
+        <v>2.488329</v>
+      </c>
+      <c r="AB31">
+        <v>0.148195120144969</v>
+      </c>
+      <c r="AC31">
+        <v>32.64503798648438</v>
       </c>
     </row>
   </sheetData>
